--- a/data/output/sim_gridrnd/ABS1/group_520_60/results/ABS1_G9_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_520_60/results/ABS1_G9_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,614 +466,702 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S03_G9_520_58_ABS1</t>
+          <t>S01_G9_519_61_ABS1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D2" t="n">
-        <v>85.9896219421794</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>509.1397091252707</v>
-      </c>
-      <c r="J2" t="n">
-        <v>53.2781897950397</v>
-      </c>
-      <c r="K2" t="n">
-        <v>514.1927471281139</v>
-      </c>
-      <c r="L2" t="n">
-        <v>47.57401733385064</v>
-      </c>
-      <c r="M2" t="n">
-        <v>520.7987389028739</v>
-      </c>
-      <c r="N2" t="n">
-        <v>41.90104789172299</v>
-      </c>
-      <c r="O2" t="n">
-        <v>521.3543165017143</v>
-      </c>
-      <c r="P2" t="n">
-        <v>45.11546459349787</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>520.6341807360526</v>
-      </c>
       <c r="R2" t="n">
-        <v>48.90768819206183</v>
+        <v>503.95</v>
       </c>
       <c r="S2" t="n">
-        <v>518.1817102512002</v>
+        <v>30.89</v>
       </c>
       <c r="T2" t="n">
-        <v>51.06582001934933</v>
+        <v>506.87</v>
       </c>
       <c r="U2" t="n">
-        <v>521.5946870446742</v>
+        <v>48.24</v>
       </c>
       <c r="V2" t="n">
-        <v>57.84816632301131</v>
+        <v>503.03</v>
       </c>
       <c r="W2" t="n">
-        <v>521.1616222089207</v>
+        <v>47.84</v>
       </c>
       <c r="X2" t="n">
-        <v>57.95529556066101</v>
+        <v>518.99</v>
       </c>
       <c r="Y2" t="n">
-        <v>521.1270564922967</v>
+        <v>68.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>57.96815722708971</v>
+        <v>520.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1578947368421053</v>
+        <v>75.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1379310344827586</v>
+        <v>519.49</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1025641025641026</v>
+        <v>69.89</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.08163265306122448</v>
+        <v>518.1799999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0847457627118644</v>
+        <v>63.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.05797101449275362</v>
+        <v>521.23</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.06329113924050633</v>
+        <v>59.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.06741573033707865</v>
+        <v>520.9299999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.06060606060606061</v>
+        <v>57.29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>513.55</v>
+        <v>0.02564102564102564</v>
       </c>
       <c r="AK2" t="n">
-        <v>512.7666666666667</v>
+        <v>0.05084745762711865</v>
       </c>
       <c r="AL2" t="n">
-        <v>514.3375</v>
+        <v>-0.01265822784810127</v>
       </c>
       <c r="AM2" t="n">
-        <v>516.11</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="AN2" t="n">
-        <v>517.8</v>
+        <v>0.1260504201680672</v>
       </c>
       <c r="AO2" t="n">
-        <v>517.4714285714285</v>
+        <v>0.1223021582733813</v>
       </c>
       <c r="AP2" t="n">
-        <v>517.975</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>519.1333333333333</v>
+        <v>0.08379888268156424</v>
       </c>
       <c r="AR2" t="n">
-        <v>519.295</v>
+        <v>0.07537688442211055</v>
       </c>
       <c r="AS2" t="n">
-        <v>54.51923972323899</v>
+        <v>502.475</v>
       </c>
       <c r="AT2" t="n">
-        <v>53.50899197538879</v>
+        <v>506.1333333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>52.61794934953281</v>
+        <v>503.0375</v>
       </c>
       <c r="AV2" t="n">
-        <v>50.90793553072055</v>
+        <v>515.87</v>
       </c>
       <c r="AW2" t="n">
-        <v>50.62058211175898</v>
+        <v>517.4083333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>50.11307825553024</v>
+        <v>518.8714285714286</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.00697868919507</v>
+        <v>517.775</v>
       </c>
       <c r="AZ2" t="n">
-        <v>52.88944444152664</v>
+        <v>517.7666666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>54.40990695636228</v>
+        <v>517.87</v>
       </c>
       <c r="BB2" t="n">
-        <v>358</v>
+        <v>44.09250928445783</v>
       </c>
       <c r="BC2" t="n">
-        <v>358</v>
+        <v>50.8105850739347</v>
       </c>
       <c r="BD2" t="n">
-        <v>358</v>
+        <v>51.498651377973</v>
       </c>
       <c r="BE2" t="n">
-        <v>358</v>
+        <v>58.05112488143534</v>
       </c>
       <c r="BF2" t="n">
-        <v>358</v>
+        <v>63.20383635947707</v>
       </c>
       <c r="BG2" t="n">
-        <v>358</v>
+        <v>66.82705214177253</v>
       </c>
       <c r="BH2" t="n">
-        <v>358</v>
+        <v>67.24990241628608</v>
       </c>
       <c r="BI2" t="n">
-        <v>358</v>
+        <v>65.85473069989396</v>
       </c>
       <c r="BJ2" t="n">
-        <v>358</v>
+        <v>64.22268368730786</v>
       </c>
       <c r="BK2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BL2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BM2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BN2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BO2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BP2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BQ2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BR2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BS2" t="n">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.8571428571428571</v>
+        <v>615</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.7777777777777778</v>
+        <v>615</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.7142857142857143</v>
+        <v>615</v>
       </c>
       <c r="BW2" t="n">
+        <v>615</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>615</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>619</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>619</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>619</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>619</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.6333333333333333</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.6857142857142857</v>
+      <c r="CE2" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>520.9299999999999</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>57.29</v>
       </c>
     </row>
     <row r="3">
@@ -1086,10 +1174,10 @@
         <v>522</v>
       </c>
       <c r="C3" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D3" t="n">
         <v>62</v>
-      </c>
-      <c r="D3" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E3" t="n">
         <v>522</v>
@@ -1098,490 +1186,556 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>476.9796239607358</v>
-      </c>
-      <c r="J3" t="n">
-        <v>70.999010837344</v>
-      </c>
-      <c r="K3" t="n">
-        <v>494.531389317765</v>
-      </c>
-      <c r="L3" t="n">
-        <v>49.92259006819058</v>
-      </c>
-      <c r="M3" t="n">
-        <v>504.9693977354789</v>
-      </c>
-      <c r="N3" t="n">
-        <v>62.76525317197902</v>
-      </c>
-      <c r="O3" t="n">
-        <v>505.9352156131835</v>
-      </c>
-      <c r="P3" t="n">
-        <v>65.14305882353545</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>518.6214816972456</v>
-      </c>
       <c r="R3" t="n">
-        <v>75.50146810820019</v>
+        <v>476.98</v>
       </c>
       <c r="S3" t="n">
-        <v>517.7483050280275</v>
+        <v>71</v>
       </c>
       <c r="T3" t="n">
-        <v>82.02661430455871</v>
+        <v>494.53</v>
       </c>
       <c r="U3" t="n">
-        <v>519.1416766749034</v>
+        <v>49.92</v>
       </c>
       <c r="V3" t="n">
-        <v>76.18696678097631</v>
+        <v>504.97</v>
       </c>
       <c r="W3" t="n">
-        <v>519.5103982892308</v>
+        <v>62.77</v>
       </c>
       <c r="X3" t="n">
-        <v>75.39577826832931</v>
+        <v>505.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>516.9290062304444</v>
+        <v>65.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>70.51005475740097</v>
+        <v>518.62</v>
       </c>
       <c r="AA3" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>82.03</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>519.14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>76.19</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>519.51</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>516.9299999999999</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AK3" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AL3" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AM3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AN3" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AO3" t="n">
         <v>0.08571428571428572</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AP3" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AQ3" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AR3" t="n">
         <v>0.04</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AS3" t="n">
         <v>477.3</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
         <v>473.1166666666667</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AU3" t="n">
         <v>491.2375</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AV3" t="n">
         <v>496.98</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AW3" t="n">
         <v>505.025</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AX3" t="n">
         <v>511.9642857142857</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AY3" t="n">
         <v>512.3875</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
         <v>513.5277777777778</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BA3" t="n">
         <v>513.37</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BB3" t="n">
         <v>64.04303240790523</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
         <v>59.62748014874424</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
         <v>63.59289342174957</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>64.26102706928982</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BF3" t="n">
         <v>67.59936667602737</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
         <v>72.35501865447756</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
         <v>73.55788430719035</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BI3" t="n">
         <v>73.76459784382835</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BJ3" t="n">
         <v>73.15205465330416</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BK3" t="n">
         <v>386</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>386</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>386</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>386</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>386</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>386</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>386</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>386</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>386</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BT3" t="n">
         <v>635</v>
       </c>
-      <c r="BL3" t="n">
+      <c r="BU3" t="n">
         <v>635</v>
       </c>
-      <c r="BM3" t="n">
+      <c r="BV3" t="n">
         <v>635</v>
       </c>
-      <c r="BN3" t="n">
+      <c r="BW3" t="n">
         <v>635</v>
       </c>
-      <c r="BO3" t="n">
+      <c r="BX3" t="n">
         <v>635</v>
       </c>
-      <c r="BP3" t="n">
+      <c r="BY3" t="n">
         <v>635</v>
       </c>
-      <c r="BQ3" t="n">
+      <c r="BZ3" t="n">
         <v>635</v>
       </c>
-      <c r="BR3" t="n">
+      <c r="CA3" t="n">
         <v>635</v>
       </c>
-      <c r="BS3" t="n">
+      <c r="CB3" t="n">
         <v>635</v>
       </c>
-      <c r="BT3" t="n">
+      <c r="CC3" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CD3" t="n">
         <v>0.6</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="CE3" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="CF3" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CH3" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CI3" t="n">
         <v>0.875</v>
       </c>
-      <c r="CA3" t="n">
+      <c r="CJ3" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="CB3" t="n">
+      <c r="CK3" t="n">
         <v>0.84</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>516.9299999999999</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S01_G9_519_61_ABS1</t>
+          <t>S03_G9_520_58_ABS1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C4" t="n">
-        <v>61</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D4" t="n">
-        <v>90.43736100815418</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>503.9504649113684</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30.88892902248049</v>
-      </c>
-      <c r="K4" t="n">
-        <v>506.865500934444</v>
-      </c>
-      <c r="L4" t="n">
-        <v>48.24272541803551</v>
-      </c>
-      <c r="M4" t="n">
-        <v>503.0332526625249</v>
-      </c>
-      <c r="N4" t="n">
-        <v>47.83939001092242</v>
-      </c>
-      <c r="O4" t="n">
-        <v>518.9890720572689</v>
-      </c>
-      <c r="P4" t="n">
-        <v>68.22379081771565</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>520.3270511902127</v>
-      </c>
       <c r="R4" t="n">
-        <v>75.43509454816889</v>
+        <v>509.14</v>
       </c>
       <c r="S4" t="n">
-        <v>519.4927900962656</v>
+        <v>53.28</v>
       </c>
       <c r="T4" t="n">
-        <v>69.88521559408215</v>
+        <v>514.1900000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>518.1759156030099</v>
+        <v>47.57</v>
       </c>
       <c r="V4" t="n">
-        <v>63.20365230592917</v>
+        <v>520.8</v>
       </c>
       <c r="W4" t="n">
-        <v>521.2301132952922</v>
+        <v>41.9</v>
       </c>
       <c r="X4" t="n">
-        <v>59.10178964742257</v>
+        <v>521.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>520.9324729539959</v>
+        <v>45.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>57.2879735693177</v>
+        <v>520.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02564102564102564</v>
+        <v>48.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05084745762711865</v>
+        <v>518.1799999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.01265822784810127</v>
+        <v>51.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1313131313131313</v>
+        <v>521.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1260504201680672</v>
+        <v>57.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1223021582733813</v>
+        <v>521.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09433962264150944</v>
+        <v>57.96</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.08379888268156424</v>
+        <v>521.13</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.07537688442211055</v>
+        <v>57.97</v>
       </c>
       <c r="AJ4" t="n">
-        <v>502.475</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="AK4" t="n">
-        <v>506.1333333333333</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="AL4" t="n">
-        <v>503.0375</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="AM4" t="n">
-        <v>515.87</v>
+        <v>0.08163265306122448</v>
       </c>
       <c r="AN4" t="n">
-        <v>517.4083333333333</v>
+        <v>0.0847457627118644</v>
       </c>
       <c r="AO4" t="n">
-        <v>518.8714285714286</v>
+        <v>0.05797101449275362</v>
       </c>
       <c r="AP4" t="n">
-        <v>517.775</v>
+        <v>0.06329113924050633</v>
       </c>
       <c r="AQ4" t="n">
-        <v>517.7666666666667</v>
+        <v>0.06741573033707865</v>
       </c>
       <c r="AR4" t="n">
-        <v>517.87</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AS4" t="n">
-        <v>44.09250928445783</v>
+        <v>513.55</v>
       </c>
       <c r="AT4" t="n">
-        <v>50.8105850739347</v>
+        <v>512.7666666666667</v>
       </c>
       <c r="AU4" t="n">
-        <v>51.498651377973</v>
+        <v>514.3375</v>
       </c>
       <c r="AV4" t="n">
-        <v>58.05112488143534</v>
+        <v>516.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>63.20383635947707</v>
+        <v>517.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>66.82705214177253</v>
+        <v>517.4714285714285</v>
       </c>
       <c r="AY4" t="n">
-        <v>67.24990241628608</v>
+        <v>517.975</v>
       </c>
       <c r="AZ4" t="n">
-        <v>65.85473069989396</v>
+        <v>519.1333333333333</v>
       </c>
       <c r="BA4" t="n">
-        <v>64.22268368730786</v>
+        <v>519.295</v>
       </c>
       <c r="BB4" t="n">
-        <v>353</v>
+        <v>54.51923972323899</v>
       </c>
       <c r="BC4" t="n">
-        <v>353</v>
+        <v>53.50899197538879</v>
       </c>
       <c r="BD4" t="n">
-        <v>353</v>
+        <v>52.61794934953281</v>
       </c>
       <c r="BE4" t="n">
-        <v>353</v>
+        <v>50.90793553072055</v>
       </c>
       <c r="BF4" t="n">
-        <v>353</v>
+        <v>50.62058211175898</v>
       </c>
       <c r="BG4" t="n">
-        <v>353</v>
+        <v>50.11307825553024</v>
       </c>
       <c r="BH4" t="n">
-        <v>353</v>
+        <v>51.00697868919507</v>
       </c>
       <c r="BI4" t="n">
-        <v>353</v>
+        <v>52.88944444152664</v>
       </c>
       <c r="BJ4" t="n">
-        <v>353</v>
+        <v>54.40990695636228</v>
       </c>
       <c r="BK4" t="n">
-        <v>615</v>
+        <v>358</v>
       </c>
       <c r="BL4" t="n">
-        <v>615</v>
+        <v>358</v>
       </c>
       <c r="BM4" t="n">
-        <v>615</v>
+        <v>358</v>
       </c>
       <c r="BN4" t="n">
-        <v>615</v>
+        <v>358</v>
       </c>
       <c r="BO4" t="n">
-        <v>615</v>
+        <v>358</v>
       </c>
       <c r="BP4" t="n">
-        <v>619</v>
+        <v>358</v>
       </c>
       <c r="BQ4" t="n">
-        <v>619</v>
+        <v>358</v>
       </c>
       <c r="BR4" t="n">
-        <v>619</v>
+        <v>358</v>
       </c>
       <c r="BS4" t="n">
-        <v>619</v>
+        <v>358</v>
       </c>
       <c r="BT4" t="n">
-        <v>1</v>
+        <v>606</v>
       </c>
       <c r="BU4" t="n">
+        <v>606</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>606</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>606</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>606</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>606</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>606</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>606</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>606</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CF4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV4" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>1</v>
+      <c r="CG4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>521.13</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>57.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G9_522_61_ABS1</t>
+          <t>S04_G9_522_58_ABS1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>61</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D5" t="n">
-        <v>90.43736100815418</v>
+        <v>58</v>
       </c>
       <c r="E5" t="n">
         <v>522</v>
@@ -1590,244 +1744,277 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>539.2146817876733</v>
-      </c>
-      <c r="J5" t="n">
-        <v>119.2019127595277</v>
-      </c>
-      <c r="K5" t="n">
-        <v>532.6289672765627</v>
-      </c>
-      <c r="L5" t="n">
-        <v>83.90293831480277</v>
-      </c>
-      <c r="M5" t="n">
-        <v>534.1715069647414</v>
-      </c>
-      <c r="N5" t="n">
-        <v>73.44640554949008</v>
-      </c>
-      <c r="O5" t="n">
-        <v>537.0129278880216</v>
-      </c>
-      <c r="P5" t="n">
-        <v>74.97724398698871</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>540.8063383466421</v>
-      </c>
       <c r="R5" t="n">
-        <v>76.40301053442806</v>
+        <v>550.5</v>
       </c>
       <c r="S5" t="n">
-        <v>545.3636775421569</v>
+        <v>54.88</v>
       </c>
       <c r="T5" t="n">
-        <v>72.56664561354789</v>
+        <v>530.39</v>
       </c>
       <c r="U5" t="n">
-        <v>542.9594428041939</v>
+        <v>74</v>
       </c>
       <c r="V5" t="n">
-        <v>71.33345227147566</v>
+        <v>532.95</v>
       </c>
       <c r="W5" t="n">
-        <v>543.1540916554973</v>
+        <v>74.14</v>
       </c>
       <c r="X5" t="n">
-        <v>69.81587002050804</v>
+        <v>528.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>546.0331687752602</v>
+        <v>66.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>70.20386699312236</v>
+        <v>526.66</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>60.21</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03333333333333333</v>
+        <v>524.58</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.025</v>
+        <v>60.77</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.02</v>
+        <v>526.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01666666666666667</v>
+        <v>61.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>524.29</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0125</v>
+        <v>58.99</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01111111111111111</v>
+        <v>517.6799999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.02</v>
+        <v>60.27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>507.7</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="AK5" t="n">
-        <v>520.75</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="AL5" t="n">
-        <v>522.525</v>
+        <v>0.1645569620253164</v>
       </c>
       <c r="AM5" t="n">
-        <v>530.0700000000001</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AN5" t="n">
-        <v>532.2166666666667</v>
+        <v>0.09243697478991597</v>
       </c>
       <c r="AO5" t="n">
-        <v>533.7142857142857</v>
+        <v>0.07913669064748201</v>
       </c>
       <c r="AP5" t="n">
-        <v>535.06875</v>
+        <v>0.06918238993710692</v>
       </c>
       <c r="AQ5" t="n">
-        <v>536.1833333333333</v>
+        <v>0.07262569832402235</v>
       </c>
       <c r="AR5" t="n">
-        <v>536.77</v>
+        <v>0.07537688442211055</v>
       </c>
       <c r="AS5" t="n">
-        <v>77.04680395707534</v>
+        <v>556.05</v>
       </c>
       <c r="AT5" t="n">
-        <v>76.94253808308292</v>
+        <v>540.2666666666667</v>
       </c>
       <c r="AU5" t="n">
-        <v>74.83715237099818</v>
+        <v>533.5125</v>
       </c>
       <c r="AV5" t="n">
-        <v>75.67526081884357</v>
+        <v>529.52</v>
       </c>
       <c r="AW5" t="n">
-        <v>75.77578585684363</v>
+        <v>529.8583333333333</v>
       </c>
       <c r="AX5" t="n">
-        <v>74.7292528029673</v>
+        <v>529.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>73.73297446487223</v>
+        <v>528.96875</v>
       </c>
       <c r="AZ5" t="n">
-        <v>72.94377400893559</v>
+        <v>529.2222222222222</v>
       </c>
       <c r="BA5" t="n">
-        <v>71.95267263972896</v>
+        <v>528.79</v>
       </c>
       <c r="BB5" t="n">
-        <v>374</v>
+        <v>48.2653861478389</v>
       </c>
       <c r="BC5" t="n">
-        <v>374</v>
+        <v>56.12363336618738</v>
       </c>
       <c r="BD5" t="n">
-        <v>374</v>
+        <v>64.96402730550193</v>
       </c>
       <c r="BE5" t="n">
-        <v>374</v>
+        <v>68.64189391326553</v>
       </c>
       <c r="BF5" t="n">
-        <v>374</v>
+        <v>67.58430486354719</v>
       </c>
       <c r="BG5" t="n">
-        <v>374</v>
+        <v>66.38068781118281</v>
       </c>
       <c r="BH5" t="n">
-        <v>374</v>
+        <v>65.06644890753989</v>
       </c>
       <c r="BI5" t="n">
-        <v>374</v>
+        <v>64.07673833039357</v>
       </c>
       <c r="BJ5" t="n">
-        <v>374</v>
+        <v>63.04606173267288</v>
       </c>
       <c r="BK5" t="n">
-        <v>621</v>
+        <v>479</v>
       </c>
       <c r="BL5" t="n">
-        <v>630</v>
+        <v>451</v>
       </c>
       <c r="BM5" t="n">
-        <v>630</v>
+        <v>434</v>
       </c>
       <c r="BN5" t="n">
-        <v>639</v>
+        <v>434</v>
       </c>
       <c r="BO5" t="n">
-        <v>639</v>
+        <v>434</v>
       </c>
       <c r="BP5" t="n">
-        <v>639</v>
+        <v>434</v>
       </c>
       <c r="BQ5" t="n">
-        <v>639</v>
+        <v>434</v>
       </c>
       <c r="BR5" t="n">
-        <v>639</v>
+        <v>434</v>
       </c>
       <c r="BS5" t="n">
-        <v>639</v>
+        <v>434</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.875</v>
+        <v>658</v>
       </c>
       <c r="BU5" t="n">
+        <v>658</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>658</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>658</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>658</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>658</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>658</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>658</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>658</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CE5" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BV5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.8260869565217391</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.8214285714285714</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.8484848484848485</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.8918918918918919</v>
+      <c r="CF5" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>517.6799999999999</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>60.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G9_522_61_ABS1</t>
+          <t>S05_G9_522_61_ABS1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>522</v>
       </c>
       <c r="C6" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D6" t="n">
         <v>61</v>
-      </c>
-      <c r="D6" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E6" t="n">
         <v>522</v>
@@ -1836,244 +2023,277 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>491.2243336459687</v>
-      </c>
-      <c r="J6" t="n">
-        <v>95.0264537409065</v>
-      </c>
-      <c r="K6" t="n">
-        <v>494.28059526117</v>
-      </c>
-      <c r="L6" t="n">
-        <v>95.51061963246397</v>
-      </c>
-      <c r="M6" t="n">
-        <v>495.0616080996897</v>
-      </c>
-      <c r="N6" t="n">
-        <v>90.88495823046027</v>
-      </c>
-      <c r="O6" t="n">
-        <v>503.4870731088723</v>
-      </c>
-      <c r="P6" t="n">
-        <v>82.64378022753201</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>514.1372873456398</v>
-      </c>
       <c r="R6" t="n">
-        <v>90.27084612836016</v>
+        <v>539.21</v>
       </c>
       <c r="S6" t="n">
-        <v>518.8867823589678</v>
+        <v>119.2</v>
       </c>
       <c r="T6" t="n">
-        <v>82.61397653583465</v>
+        <v>532.63</v>
       </c>
       <c r="U6" t="n">
-        <v>522.6532531539447</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>79.81806191810097</v>
+        <v>534.17</v>
       </c>
       <c r="W6" t="n">
-        <v>523.7971402436633</v>
+        <v>73.45</v>
       </c>
       <c r="X6" t="n">
-        <v>79.34599137397568</v>
+        <v>537.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>524.4434455286458</v>
+        <v>74.98</v>
       </c>
       <c r="Z6" t="n">
-        <v>78.30614946980525</v>
+        <v>540.8099999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.05</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AB6" t="n">
+        <v>545.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>542.96</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>543.15</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>546.03</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AK6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="AO6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>490.675</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>493.6166666666667</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>494.65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>499.02</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>503.9166666666667</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>507.4714285714286</v>
-      </c>
       <c r="AP6" t="n">
-        <v>508.61875</v>
+        <v>-0.0125</v>
       </c>
       <c r="AQ6" t="n">
-        <v>509.6555555555556</v>
+        <v>-0.01111111111111111</v>
       </c>
       <c r="AR6" t="n">
-        <v>511.695</v>
+        <v>-0.02</v>
       </c>
       <c r="AS6" t="n">
-        <v>57.79852398634415</v>
+        <v>507.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>68.26445919282513</v>
+        <v>520.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>73.85054163647007</v>
+        <v>522.525</v>
       </c>
       <c r="AV6" t="n">
-        <v>76.50921251718646</v>
+        <v>530.0700000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>78.28660840498556</v>
+        <v>532.2166666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>80.38536139453882</v>
+        <v>533.7142857142857</v>
       </c>
       <c r="AY6" t="n">
-        <v>80.89614266723414</v>
+        <v>535.06875</v>
       </c>
       <c r="AZ6" t="n">
-        <v>80.80953754368782</v>
+        <v>536.1833333333333</v>
       </c>
       <c r="BA6" t="n">
-        <v>79.87378778422868</v>
+        <v>536.77</v>
       </c>
       <c r="BB6" t="n">
-        <v>353</v>
+        <v>77.04680395707534</v>
       </c>
       <c r="BC6" t="n">
-        <v>353</v>
+        <v>76.94253808308292</v>
       </c>
       <c r="BD6" t="n">
-        <v>353</v>
+        <v>74.83715237099818</v>
       </c>
       <c r="BE6" t="n">
-        <v>353</v>
+        <v>75.67526081884357</v>
       </c>
       <c r="BF6" t="n">
-        <v>353</v>
+        <v>75.77578585684363</v>
       </c>
       <c r="BG6" t="n">
-        <v>353</v>
+        <v>74.7292528029673</v>
       </c>
       <c r="BH6" t="n">
-        <v>353</v>
+        <v>73.73297446487223</v>
       </c>
       <c r="BI6" t="n">
-        <v>353</v>
+        <v>72.94377400893559</v>
       </c>
       <c r="BJ6" t="n">
-        <v>353</v>
+        <v>71.95267263972896</v>
       </c>
       <c r="BK6" t="n">
-        <v>576</v>
+        <v>374</v>
       </c>
       <c r="BL6" t="n">
-        <v>587</v>
+        <v>374</v>
       </c>
       <c r="BM6" t="n">
-        <v>599</v>
+        <v>374</v>
       </c>
       <c r="BN6" t="n">
-        <v>599</v>
+        <v>374</v>
       </c>
       <c r="BO6" t="n">
-        <v>615</v>
+        <v>374</v>
       </c>
       <c r="BP6" t="n">
-        <v>620</v>
+        <v>374</v>
       </c>
       <c r="BQ6" t="n">
-        <v>620</v>
+        <v>374</v>
       </c>
       <c r="BR6" t="n">
+        <v>374</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>374</v>
+      </c>
+      <c r="BT6" t="n">
         <v>621</v>
       </c>
-      <c r="BS6" t="n">
-        <v>621</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="BU6" t="n">
-        <v>0.75</v>
+        <v>630</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9090909090909091</v>
+        <v>630</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.9285714285714286</v>
+        <v>639</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.8888888888888888</v>
+        <v>639</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.8181818181818182</v>
+        <v>639</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.7826086956521739</v>
+        <v>639</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.8846153846153846</v>
+        <v>639</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.8275862068965517</v>
+        <v>639</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.8918918918918919</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>546.03</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>70.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S04_G9_522_58_ABS1</t>
+          <t>S06_G9_522_61_ABS1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>522</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D7" t="n">
-        <v>85.9896219421794</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>522</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>550.5012854446552</v>
-      </c>
-      <c r="J7" t="n">
-        <v>54.87676088836963</v>
-      </c>
-      <c r="K7" t="n">
-        <v>530.3929611178081</v>
-      </c>
-      <c r="L7" t="n">
-        <v>74.00018777280066</v>
-      </c>
-      <c r="M7" t="n">
-        <v>532.9469294288344</v>
-      </c>
-      <c r="N7" t="n">
-        <v>74.14172572999284</v>
-      </c>
-      <c r="O7" t="n">
-        <v>528.3510904965156</v>
-      </c>
-      <c r="P7" t="n">
-        <v>66.49562202556099</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>526.6574024872373</v>
-      </c>
       <c r="R7" t="n">
-        <v>60.21334873337641</v>
+        <v>491.22</v>
       </c>
       <c r="S7" t="n">
-        <v>524.5791927871703</v>
+        <v>95.03</v>
       </c>
       <c r="T7" t="n">
-        <v>60.77205375264758</v>
+        <v>494.28</v>
       </c>
       <c r="U7" t="n">
-        <v>526.6040232285177</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>61.49689542523155</v>
+        <v>495.06</v>
       </c>
       <c r="W7" t="n">
-        <v>524.2886013211202</v>
+        <v>90.88</v>
       </c>
       <c r="X7" t="n">
-        <v>58.99441985272467</v>
+        <v>503.49</v>
       </c>
       <c r="Y7" t="n">
-        <v>517.6817442852267</v>
+        <v>82.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>60.2673420645655</v>
+        <v>514.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6410256410256411</v>
+        <v>90.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.288135593220339</v>
+        <v>518.89</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1645569620253164</v>
+        <v>82.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.09090909090909091</v>
+        <v>522.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.09243697478991597</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.07913669064748201</v>
+        <v>523.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.06918238993710692</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.07262569832402235</v>
+        <v>524.4400000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.07537688442211055</v>
+        <v>78.31</v>
       </c>
       <c r="AJ7" t="n">
-        <v>556.05</v>
+        <v>-0.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>540.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>533.5125</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>529.52</v>
+        <v>0.04</v>
       </c>
       <c r="AN7" t="n">
-        <v>529.8583333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AO7" t="n">
-        <v>529.3</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="AP7" t="n">
-        <v>528.96875</v>
+        <v>0.05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>529.2222222222222</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="AR7" t="n">
-        <v>528.79</v>
+        <v>0.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>48.2653861478389</v>
+        <v>490.675</v>
       </c>
       <c r="AT7" t="n">
-        <v>56.12363336618738</v>
+        <v>493.6166666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>64.96402730550193</v>
+        <v>494.65</v>
       </c>
       <c r="AV7" t="n">
-        <v>68.64189391326553</v>
+        <v>499.02</v>
       </c>
       <c r="AW7" t="n">
-        <v>67.58430486354719</v>
+        <v>503.9166666666667</v>
       </c>
       <c r="AX7" t="n">
-        <v>66.38068781118281</v>
+        <v>507.4714285714286</v>
       </c>
       <c r="AY7" t="n">
-        <v>65.06644890753989</v>
+        <v>508.61875</v>
       </c>
       <c r="AZ7" t="n">
-        <v>64.07673833039357</v>
+        <v>509.6555555555556</v>
       </c>
       <c r="BA7" t="n">
-        <v>63.04606173267288</v>
+        <v>511.695</v>
       </c>
       <c r="BB7" t="n">
-        <v>479</v>
+        <v>57.79852398634415</v>
       </c>
       <c r="BC7" t="n">
-        <v>451</v>
+        <v>68.26445919282513</v>
       </c>
       <c r="BD7" t="n">
-        <v>434</v>
+        <v>73.85054163647007</v>
       </c>
       <c r="BE7" t="n">
-        <v>434</v>
+        <v>76.50921251718646</v>
       </c>
       <c r="BF7" t="n">
-        <v>434</v>
+        <v>78.28660840498556</v>
       </c>
       <c r="BG7" t="n">
-        <v>434</v>
+        <v>80.38536139453882</v>
       </c>
       <c r="BH7" t="n">
-        <v>434</v>
+        <v>80.89614266723414</v>
       </c>
       <c r="BI7" t="n">
-        <v>434</v>
+        <v>80.80953754368782</v>
       </c>
       <c r="BJ7" t="n">
-        <v>434</v>
+        <v>79.87378778422868</v>
       </c>
       <c r="BK7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BL7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BM7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BN7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BO7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BP7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BQ7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BR7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BS7" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.8</v>
+        <v>576</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.7777777777777778</v>
+        <v>587</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.5833333333333334</v>
+        <v>599</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.4666666666666667</v>
+        <v>599</v>
       </c>
       <c r="BX7" t="n">
+        <v>615</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>620</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>620</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>621</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>621</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CD7" t="n">
         <v>0.75</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CE7" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CG7" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>1</v>
+      <c r="CH7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>524.4400000000001</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>78.31</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>522</v>
       </c>
       <c r="C8" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D8" t="n">
         <v>60</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E8" t="n">
         <v>522</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>557.5693893044264</v>
-      </c>
-      <c r="J8" t="n">
-        <v>68.94923783666668</v>
-      </c>
-      <c r="K8" t="n">
-        <v>522.1164050450641</v>
-      </c>
-      <c r="L8" t="n">
-        <v>91.86537124705762</v>
-      </c>
-      <c r="M8" t="n">
-        <v>517.0128942090942</v>
-      </c>
-      <c r="N8" t="n">
-        <v>79.76487207221275</v>
-      </c>
-      <c r="O8" t="n">
-        <v>512.1671743911338</v>
-      </c>
-      <c r="P8" t="n">
-        <v>76.19824664747213</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>514.0098632852746</v>
-      </c>
       <c r="R8" t="n">
-        <v>71.15049288472019</v>
+        <v>557.5700000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>506.3970950631721</v>
+        <v>68.95</v>
       </c>
       <c r="T8" t="n">
-        <v>72.21913470656932</v>
+        <v>522.12</v>
       </c>
       <c r="U8" t="n">
-        <v>502.3720826987559</v>
+        <v>91.87</v>
       </c>
       <c r="V8" t="n">
-        <v>73.90251077752049</v>
+        <v>517.01</v>
       </c>
       <c r="W8" t="n">
-        <v>506.1718648914966</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>70.10313012785787</v>
+        <v>512.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>509.1726891425756</v>
+        <v>76.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>68.20247270417107</v>
+        <v>514.01</v>
       </c>
       <c r="AA8" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>506.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>502.37</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>506.17</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>509.17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>0.45</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v>0.08</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v>0.06</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AS8" t="n">
         <v>557.475</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>535.7</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>531.15</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>526.7</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>525.5166666666667</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>523.3785714285714</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>519.45625</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>517.4</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>516.09</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>75.85149553568472</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>79.72291598614123</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>80.86518101135989</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>81.92051025231714</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>79.82720748939897</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>78.07207913727115</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>77.80704072214481</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>76.63510944730228</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>75.18571606362474</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>371</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>371</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>371</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>371</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>371</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>371</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>371</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>371</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>371</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>702</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>702</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>702</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>702</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>702</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>702</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>702</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>702</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>702</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>1</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.5625</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.96</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.9310344827586207</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.8484848484848485</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>509.17</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>68.2</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>519</v>
       </c>
       <c r="C9" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D9" t="n">
         <v>59</v>
-      </c>
-      <c r="D9" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E9" t="n">
         <v>519</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>72.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>531.4169230774382</v>
-      </c>
-      <c r="J9" t="n">
-        <v>45.98645544026806</v>
-      </c>
-      <c r="K9" t="n">
-        <v>527.5247243374034</v>
-      </c>
-      <c r="L9" t="n">
-        <v>55.15158785631468</v>
-      </c>
-      <c r="M9" t="n">
-        <v>520.855251737445</v>
-      </c>
-      <c r="N9" t="n">
-        <v>53.72209400217573</v>
-      </c>
-      <c r="O9" t="n">
-        <v>523.5926565463143</v>
-      </c>
-      <c r="P9" t="n">
-        <v>57.29325189998947</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>522.811727096353</v>
-      </c>
       <c r="R9" t="n">
-        <v>67.82610147137646</v>
+        <v>531.42</v>
       </c>
       <c r="S9" t="n">
-        <v>523.4617186160206</v>
+        <v>45.99</v>
       </c>
       <c r="T9" t="n">
-        <v>69.070035252542</v>
+        <v>527.52</v>
       </c>
       <c r="U9" t="n">
-        <v>525.1095968362621</v>
+        <v>55.15</v>
       </c>
       <c r="V9" t="n">
-        <v>78.71957540783976</v>
+        <v>520.86</v>
       </c>
       <c r="W9" t="n">
-        <v>527.6062410740127</v>
+        <v>53.72</v>
       </c>
       <c r="X9" t="n">
-        <v>86.76064047987417</v>
+        <v>523.59</v>
       </c>
       <c r="Y9" t="n">
-        <v>526.4898007539391</v>
+        <v>57.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>91.53473309872081</v>
+        <v>522.8099999999999</v>
       </c>
       <c r="AA9" t="n">
+        <v>67.83</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>523.46</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>69.06999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>525.11</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>527.61</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>86.76000000000001</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>526.49</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v>0.075</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v>0.05</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v>0.02857142857142857</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v>0.0375</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v>0.04</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
         <v>525.4</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>523.5333333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>523.975</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>523.5599999999999</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>522.7666666666667</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>521.5571428571428</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>523.20625</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>525.6277777777777</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>524.765</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>54.95443567174537</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>59.49046608958074</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>58.60524187306115</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>59.94219215210601</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>60.38884186852918</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>63.59203357885229</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>66.14681557669651</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>69.73585324920791</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>73.75398141795466</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>390</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>390</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>390</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>390</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>390</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>390</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>390</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>390</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>390</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>645</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>645</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>645</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>645</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>645</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>645</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>645</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>645</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>648</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.625</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.875</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>526.49</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>91.53</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>519</v>
       </c>
       <c r="C10" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D10" t="n">
         <v>60</v>
-      </c>
-      <c r="D10" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E10" t="n">
         <v>519</v>
@@ -2820,720 +3139,819 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>544.9525313551569</v>
-      </c>
-      <c r="J10" t="n">
-        <v>177.0408881851273</v>
-      </c>
-      <c r="K10" t="n">
-        <v>556.7500315069921</v>
-      </c>
-      <c r="L10" t="n">
-        <v>103.8614953430585</v>
-      </c>
-      <c r="M10" t="n">
-        <v>547.8208022872232</v>
-      </c>
-      <c r="N10" t="n">
-        <v>91.57794728138911</v>
-      </c>
-      <c r="O10" t="n">
-        <v>540.7734459990749</v>
-      </c>
-      <c r="P10" t="n">
-        <v>80.99459380948279</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>541.5512366046561</v>
-      </c>
       <c r="R10" t="n">
-        <v>81.53943364942793</v>
+        <v>544.95</v>
       </c>
       <c r="S10" t="n">
-        <v>532.1387289083254</v>
+        <v>177.04</v>
       </c>
       <c r="T10" t="n">
-        <v>93.02241236157994</v>
+        <v>556.75</v>
       </c>
       <c r="U10" t="n">
-        <v>532.1644812341884</v>
+        <v>103.86</v>
       </c>
       <c r="V10" t="n">
-        <v>86.2731843095917</v>
+        <v>547.8200000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>525.9064549477479</v>
+        <v>91.58</v>
       </c>
       <c r="X10" t="n">
-        <v>87.25738549957211</v>
+        <v>540.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>526.3750883829837</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>79.79549028425031</v>
+        <v>541.55</v>
       </c>
       <c r="AA10" t="n">
+        <v>81.54000000000001</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>532.14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>532.16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>525.91</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>87.26000000000001</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>526.38</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>0.4576271186440678</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>0.2658227848101266</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>0.1919191919191919</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>0.1764705882352941</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>0.09352517985611511</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>0.08176100628930817</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>0.07262569832402235</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>0.08542713567839195</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>573.375</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>563.9833333333333</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>553.8875</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>549.4299999999999</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>548.3916666666667</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>541.7285714285714</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>540.54375</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>539.5333333333333</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>539.8099999999999</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>68.34789224987117</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>71.04071406985966</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>77.04105946668957</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>80.39779288015312</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>79.75528152138612</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>81.5066905980417</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>83.21484594672697</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>83.01066865837855</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>82.64704410927229</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>482</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>461</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>445</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>437</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>437</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>428</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>428</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>428</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>428</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>717</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>717</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>717</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>717</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>717</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>717</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>717</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>717</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>717</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>1</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>1</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.1176470588235294</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.6785714285714286</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.6923076923076923</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>526.38</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>79.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S11_G9_521_59_ABS1</t>
+          <t>S10_G9_522_60_ABS1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D11" t="n">
-        <v>87.47220163083766</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>72.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>501.0367424220009</v>
-      </c>
-      <c r="J11" t="n">
-        <v>72.35306010682001</v>
-      </c>
-      <c r="K11" t="n">
-        <v>511.6683842964563</v>
-      </c>
-      <c r="L11" t="n">
-        <v>56.14259040216869</v>
-      </c>
-      <c r="M11" t="n">
-        <v>511.2087494836011</v>
-      </c>
-      <c r="N11" t="n">
-        <v>65.26977736352958</v>
-      </c>
-      <c r="O11" t="n">
-        <v>505.9126386027328</v>
-      </c>
-      <c r="P11" t="n">
-        <v>64.36395321358165</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>510.495972396653</v>
-      </c>
       <c r="R11" t="n">
-        <v>65.2819995491227</v>
+        <v>520.74</v>
       </c>
       <c r="S11" t="n">
-        <v>518.3816942978165</v>
+        <v>60.06</v>
       </c>
       <c r="T11" t="n">
-        <v>68.561141147752</v>
+        <v>527.87</v>
       </c>
       <c r="U11" t="n">
-        <v>516.7698468832994</v>
+        <v>46.94</v>
       </c>
       <c r="V11" t="n">
-        <v>69.66416843386823</v>
+        <v>525.89</v>
       </c>
       <c r="W11" t="n">
-        <v>514.8585691213533</v>
+        <v>46.65</v>
       </c>
       <c r="X11" t="n">
-        <v>71.3093564737711</v>
+        <v>519.84</v>
       </c>
       <c r="Y11" t="n">
-        <v>515.387109315753</v>
+        <v>50.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>67.81890636939595</v>
+        <v>521.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.05</v>
+        <v>41.95</v>
       </c>
       <c r="AB11" t="n">
+        <v>520.34</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>516.76</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>512.96</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>511.35</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.1857142857142857</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.02857142857142857</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.02222222222222222</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>509.7</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>508.3833333333333</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>511.75</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>509.45</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>510.8083333333333</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>512.1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>513.0625</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>513.2055555555555</v>
-      </c>
       <c r="AR11" t="n">
-        <v>512.625</v>
+        <v>0.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>64.90654820586286</v>
+        <v>501.35</v>
       </c>
       <c r="AT11" t="n">
-        <v>64.57633510470809</v>
+        <v>511.3666666666667</v>
       </c>
       <c r="AU11" t="n">
-        <v>62.90955809731936</v>
+        <v>513.9625</v>
       </c>
       <c r="AV11" t="n">
-        <v>63.95301009334901</v>
+        <v>514.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>65.40289186181975</v>
+        <v>515.7833333333333</v>
       </c>
       <c r="AX11" t="n">
-        <v>65.48776330626312</v>
+        <v>517.3642857142858</v>
       </c>
       <c r="AY11" t="n">
-        <v>66.12201670964068</v>
+        <v>515.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>66.85495886388203</v>
+        <v>511.6555555555556</v>
       </c>
       <c r="BA11" t="n">
-        <v>67.62591496608383</v>
+        <v>512.15</v>
       </c>
       <c r="BB11" t="n">
-        <v>421</v>
+        <v>73.20845238085558</v>
       </c>
       <c r="BC11" t="n">
-        <v>421</v>
+        <v>63.87800003826739</v>
       </c>
       <c r="BD11" t="n">
-        <v>421</v>
+        <v>57.98651648228233</v>
       </c>
       <c r="BE11" t="n">
-        <v>421</v>
+        <v>55.82006807591693</v>
       </c>
       <c r="BF11" t="n">
-        <v>421</v>
+        <v>53.81328574081147</v>
       </c>
       <c r="BG11" t="n">
-        <v>421</v>
+        <v>51.51077705743939</v>
       </c>
       <c r="BH11" t="n">
-        <v>421</v>
+        <v>49.59634563150797</v>
       </c>
       <c r="BI11" t="n">
-        <v>421</v>
+        <v>49.56099745904841</v>
       </c>
       <c r="BJ11" t="n">
-        <v>421</v>
+        <v>49.32613404677078</v>
       </c>
       <c r="BK11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BL11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BM11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BN11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BO11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BP11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BQ11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BR11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BS11" t="n">
-        <v>648</v>
+        <v>294</v>
       </c>
       <c r="BT11" t="n">
+        <v>638</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>638</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>638</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>638</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>638</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>638</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>638</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>638</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>638</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CG11" t="n">
         <v>1</v>
       </c>
-      <c r="BU11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>0.9545454545454546</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>0.9393939393939394</v>
+      <c r="CH11" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.9302325581395349</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>511.35</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>46.77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S10_G9_522_60_ABS1</t>
+          <t>S11_G9_521_59_ABS1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C12" t="n">
-        <v>60</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D12" t="n">
-        <v>88.95478131949592</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F12" t="n">
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>520.737950912714</v>
-      </c>
-      <c r="J12" t="n">
-        <v>60.06425609993769</v>
-      </c>
-      <c r="K12" t="n">
-        <v>527.8737824174565</v>
-      </c>
-      <c r="L12" t="n">
-        <v>46.94275319087334</v>
-      </c>
-      <c r="M12" t="n">
-        <v>525.8872194620142</v>
-      </c>
-      <c r="N12" t="n">
-        <v>46.6527881844963</v>
-      </c>
-      <c r="O12" t="n">
-        <v>519.8373623653305</v>
-      </c>
-      <c r="P12" t="n">
-        <v>50.63235856981338</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>521.8508882889986</v>
-      </c>
       <c r="R12" t="n">
-        <v>41.94539340943757</v>
+        <v>501.04</v>
       </c>
       <c r="S12" t="n">
-        <v>520.3352180176112</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>37.072441547166</v>
+        <v>511.67</v>
       </c>
       <c r="U12" t="n">
-        <v>516.7647332973957</v>
+        <v>56.14</v>
       </c>
       <c r="V12" t="n">
-        <v>41.38164470320083</v>
+        <v>511.21</v>
       </c>
       <c r="W12" t="n">
-        <v>512.9579023722602</v>
+        <v>65.27</v>
       </c>
       <c r="X12" t="n">
-        <v>47.73188832724419</v>
+        <v>505.91</v>
       </c>
       <c r="Y12" t="n">
-        <v>511.3474842395005</v>
+        <v>64.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>46.76680291539485</v>
+        <v>510.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2</v>
+        <v>65.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3666666666666666</v>
+        <v>518.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.275</v>
+        <v>68.56</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2</v>
+        <v>516.77</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1833333333333333</v>
+        <v>69.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1857142857142857</v>
+        <v>514.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.125</v>
+        <v>71.31</v>
       </c>
       <c r="AH12" t="n">
+        <v>515.39</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK12" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AI12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>501.35</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>511.3666666666667</v>
-      </c>
       <c r="AL12" t="n">
-        <v>513.9625</v>
+        <v>0.025</v>
       </c>
       <c r="AM12" t="n">
-        <v>514.4</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>515.7833333333333</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="AO12" t="n">
-        <v>517.3642857142858</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="AP12" t="n">
-        <v>515.8</v>
+        <v>0.025</v>
       </c>
       <c r="AQ12" t="n">
-        <v>511.6555555555556</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="AR12" t="n">
-        <v>512.15</v>
+        <v>0.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>73.20845238085558</v>
+        <v>509.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>63.87800003826739</v>
+        <v>508.3833333333333</v>
       </c>
       <c r="AU12" t="n">
-        <v>57.98651648228233</v>
+        <v>511.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>55.82006807591693</v>
+        <v>509.45</v>
       </c>
       <c r="AW12" t="n">
-        <v>53.81328574081147</v>
+        <v>510.8083333333333</v>
       </c>
       <c r="AX12" t="n">
-        <v>51.51077705743939</v>
+        <v>512.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>49.59634563150797</v>
+        <v>513.0625</v>
       </c>
       <c r="AZ12" t="n">
-        <v>49.56099745904841</v>
+        <v>513.2055555555555</v>
       </c>
       <c r="BA12" t="n">
-        <v>49.32613404677078</v>
+        <v>512.625</v>
       </c>
       <c r="BB12" t="n">
-        <v>294</v>
+        <v>64.90654820586286</v>
       </c>
       <c r="BC12" t="n">
-        <v>294</v>
+        <v>64.57633510470809</v>
       </c>
       <c r="BD12" t="n">
-        <v>294</v>
+        <v>62.90955809731936</v>
       </c>
       <c r="BE12" t="n">
-        <v>294</v>
+        <v>63.95301009334901</v>
       </c>
       <c r="BF12" t="n">
-        <v>294</v>
+        <v>65.40289186181975</v>
       </c>
       <c r="BG12" t="n">
-        <v>294</v>
+        <v>65.48776330626312</v>
       </c>
       <c r="BH12" t="n">
-        <v>294</v>
+        <v>66.12201670964068</v>
       </c>
       <c r="BI12" t="n">
-        <v>294</v>
+        <v>66.85495886388203</v>
       </c>
       <c r="BJ12" t="n">
-        <v>294</v>
+        <v>67.62591496608383</v>
       </c>
       <c r="BK12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BL12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BM12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BN12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BO12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BP12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BQ12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BR12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BS12" t="n">
-        <v>638</v>
+        <v>421</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.7142857142857143</v>
+        <v>648</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.6666666666666666</v>
+        <v>648</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.75</v>
+        <v>648</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.8888888888888888</v>
+        <v>648</v>
       </c>
       <c r="BX12" t="n">
+        <v>648</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>648</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>648</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>648</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>648</v>
+      </c>
+      <c r="CC12" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" t="n">
-        <v>0.9310344827586207</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0.9696969696969697</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0.9714285714285714</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>0.9302325581395349</v>
+      <c r="CD12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>515.39</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>522</v>
       </c>
       <c r="C13" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D13" t="n">
         <v>59</v>
-      </c>
-      <c r="D13" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E13" t="n">
         <v>522</v>
@@ -3558,720 +3976,819 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>544.1428536009726</v>
-      </c>
-      <c r="J13" t="n">
-        <v>68.94140242684487</v>
-      </c>
-      <c r="K13" t="n">
-        <v>536.5302754782446</v>
-      </c>
-      <c r="L13" t="n">
-        <v>57.27309821771973</v>
-      </c>
-      <c r="M13" t="n">
-        <v>538.6961861977177</v>
-      </c>
-      <c r="N13" t="n">
-        <v>62.90122160640483</v>
-      </c>
-      <c r="O13" t="n">
-        <v>532.4730698247586</v>
-      </c>
-      <c r="P13" t="n">
-        <v>70.38201467362352</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>534.1518724066832</v>
-      </c>
       <c r="R13" t="n">
-        <v>67.77047610431366</v>
+        <v>544.14</v>
       </c>
       <c r="S13" t="n">
-        <v>532.226826106235</v>
+        <v>68.94</v>
       </c>
       <c r="T13" t="n">
-        <v>63.61466134455648</v>
+        <v>536.53</v>
       </c>
       <c r="U13" t="n">
-        <v>529.3991016193967</v>
+        <v>57.27</v>
       </c>
       <c r="V13" t="n">
-        <v>60.37709736978367</v>
+        <v>538.7</v>
       </c>
       <c r="W13" t="n">
-        <v>526.8440094887375</v>
+        <v>62.9</v>
       </c>
       <c r="X13" t="n">
-        <v>59.38623704506308</v>
+        <v>532.47</v>
       </c>
       <c r="Y13" t="n">
-        <v>527.9488046340828</v>
+        <v>70.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>61.07322915352468</v>
+        <v>534.15</v>
       </c>
       <c r="AA13" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>532.23</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>529.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>526.84</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>527.95</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>0.3898305084745763</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
         <v>0.3164556962025317</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AM13" t="n">
         <v>0.1919191919191919</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AN13" t="n">
         <v>0.1764705882352941</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AO13" t="n">
         <v>0.1510791366906475</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AP13" t="n">
         <v>0.1446540880503145</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AQ13" t="n">
         <v>0.1620111731843575</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AR13" t="n">
         <v>0.1256281407035176</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
         <v>544.725</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>536.85</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>538.6625</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>533.04</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>534.3833333333333</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>534.4857142857143</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>534.6</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>535.3888888888889</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>533.36</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>41.19525913257495</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>55.96064837603891</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>59.42515118828054</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>63.50384555284821</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>66.63747485878766</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>65.77705697650052</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>64.55426012278353</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>63.39614331845685</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>63.04466987779379</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>483</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>443</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>443</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>442</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>439</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>439</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>439</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>439</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>439</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>630</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>630</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>630</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>630</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>630</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>630</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>630</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>630</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>630</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.6</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.75</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.9</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.9545454545454546</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>527.95</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>61.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G9_522_59_ABS1</t>
+          <t>S13_G9_518_61_ABS1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C14" t="n">
-        <v>59</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D14" t="n">
-        <v>87.47220163083766</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>498.7577468041738</v>
-      </c>
-      <c r="J14" t="n">
-        <v>38.698121333048</v>
-      </c>
-      <c r="K14" t="n">
-        <v>500.5864707058078</v>
-      </c>
-      <c r="L14" t="n">
-        <v>68.59099127721967</v>
-      </c>
-      <c r="M14" t="n">
-        <v>507.8331223462544</v>
-      </c>
-      <c r="N14" t="n">
-        <v>80.67169910893217</v>
-      </c>
-      <c r="O14" t="n">
-        <v>505.2689863716998</v>
-      </c>
-      <c r="P14" t="n">
-        <v>74.6460890455544</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>504.3984986510561</v>
-      </c>
       <c r="R14" t="n">
-        <v>66.0221244332549</v>
+        <v>534.39</v>
       </c>
       <c r="S14" t="n">
-        <v>510.1350293642849</v>
+        <v>48.06</v>
       </c>
       <c r="T14" t="n">
-        <v>66.81269692513921</v>
+        <v>548.76</v>
       </c>
       <c r="U14" t="n">
-        <v>512.473345941419</v>
+        <v>79.27</v>
       </c>
       <c r="V14" t="n">
-        <v>59.84456313284595</v>
+        <v>540.65</v>
       </c>
       <c r="W14" t="n">
-        <v>512.3939957986232</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>57.74900585400325</v>
+        <v>532.92</v>
       </c>
       <c r="Y14" t="n">
-        <v>514.822058546538</v>
+        <v>101</v>
       </c>
       <c r="Z14" t="n">
-        <v>57.61958226229441</v>
+        <v>532.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.03448275862068965</v>
+        <v>527.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.05128205128205128</v>
+        <v>86.73</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.02040816326530612</v>
+        <v>523.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.03389830508474576</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.04347826086956522</v>
+        <v>520.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.02531645569620253</v>
+        <v>78.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.02247191011235955</v>
+        <v>520.08</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0101010101010101</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="AJ14" t="n">
-        <v>504.275</v>
+        <v>0.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>501.4</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="AL14" t="n">
-        <v>508.0375</v>
+        <v>0.25</v>
       </c>
       <c r="AM14" t="n">
-        <v>505.44</v>
+        <v>0.14</v>
       </c>
       <c r="AN14" t="n">
-        <v>506.7416666666667</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="AO14" t="n">
-        <v>507.7571428571429</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="AP14" t="n">
-        <v>507.16875</v>
+        <v>0.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>507.7277777777778</v>
+        <v>0.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>508.085</v>
+        <v>0.11</v>
       </c>
       <c r="AS14" t="n">
-        <v>35.69733008223444</v>
+        <v>529.375</v>
       </c>
       <c r="AT14" t="n">
-        <v>49.55542351751219</v>
+        <v>543.4333333333333</v>
       </c>
       <c r="AU14" t="n">
-        <v>59.48853749883249</v>
+        <v>540.475</v>
       </c>
       <c r="AV14" t="n">
-        <v>66.30736309038386</v>
+        <v>533.17</v>
       </c>
       <c r="AW14" t="n">
-        <v>67.38613801979025</v>
+        <v>532.825</v>
       </c>
       <c r="AX14" t="n">
-        <v>67.14747856435876</v>
+        <v>530.8214285714286</v>
       </c>
       <c r="AY14" t="n">
-        <v>66.27784526851714</v>
+        <v>531.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>64.69645624466061</v>
+        <v>531.35</v>
       </c>
       <c r="BA14" t="n">
-        <v>63.18574028212378</v>
+        <v>531.21</v>
       </c>
       <c r="BB14" t="n">
-        <v>446</v>
+        <v>53.13599886141221</v>
       </c>
       <c r="BC14" t="n">
-        <v>417</v>
+        <v>58.50480512079518</v>
       </c>
       <c r="BD14" t="n">
-        <v>410</v>
+        <v>68.79152836650745</v>
       </c>
       <c r="BE14" t="n">
-        <v>401</v>
+        <v>76.21339186783382</v>
       </c>
       <c r="BF14" t="n">
-        <v>401</v>
+        <v>79.16161343521661</v>
       </c>
       <c r="BG14" t="n">
-        <v>401</v>
+        <v>80.79058182885488</v>
       </c>
       <c r="BH14" t="n">
-        <v>401</v>
+        <v>81.20535696615094</v>
       </c>
       <c r="BI14" t="n">
-        <v>401</v>
+        <v>80.06937790302719</v>
       </c>
       <c r="BJ14" t="n">
-        <v>401</v>
+        <v>78.72735166382775</v>
       </c>
       <c r="BK14" t="n">
-        <v>632</v>
+        <v>451</v>
       </c>
       <c r="BL14" t="n">
-        <v>632</v>
+        <v>451</v>
       </c>
       <c r="BM14" t="n">
-        <v>632</v>
+        <v>438</v>
       </c>
       <c r="BN14" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="BO14" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="BP14" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="BQ14" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="BR14" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="BS14" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="BT14" t="n">
+        <v>644</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>644</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>651</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>651</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>651</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>651</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>651</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>651</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>651</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD14" t="n">
         <v>1</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CE14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CI14" t="n">
         <v>1</v>
       </c>
-      <c r="BV14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BW14" t="n">
+      <c r="CJ14" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BX14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0.9473684210526315</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>0.6666666666666666</v>
+      <c r="CK14" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>520.08</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>72.34999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S13_G9_518_61_ABS1</t>
+          <t>S14_G9_522_59_ABS1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D15" t="n">
-        <v>90.43736100815418</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>534.3881263684482</v>
-      </c>
-      <c r="J15" t="n">
-        <v>48.05799822232793</v>
-      </c>
-      <c r="K15" t="n">
-        <v>548.7565134390136</v>
-      </c>
-      <c r="L15" t="n">
-        <v>79.27468572824226</v>
-      </c>
-      <c r="M15" t="n">
-        <v>540.6495495387395</v>
-      </c>
-      <c r="N15" t="n">
-        <v>95.57246683831944</v>
-      </c>
-      <c r="O15" t="n">
-        <v>532.9170333593597</v>
-      </c>
-      <c r="P15" t="n">
-        <v>100.9983158940003</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>532.5992222575769</v>
-      </c>
       <c r="R15" t="n">
-        <v>88.49502203148398</v>
+        <v>498.76</v>
       </c>
       <c r="S15" t="n">
-        <v>527.7981215788589</v>
+        <v>38.7</v>
       </c>
       <c r="T15" t="n">
-        <v>86.73103376657862</v>
+        <v>500.59</v>
       </c>
       <c r="U15" t="n">
-        <v>523.1665384475235</v>
+        <v>68.59</v>
       </c>
       <c r="V15" t="n">
-        <v>77.96356503799724</v>
+        <v>507.83</v>
       </c>
       <c r="W15" t="n">
-        <v>520.0057985824558</v>
+        <v>80.67</v>
       </c>
       <c r="X15" t="n">
-        <v>78.37170136622773</v>
+        <v>505.27</v>
       </c>
       <c r="Y15" t="n">
-        <v>520.0788741923778</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>72.34521814550546</v>
+        <v>504.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.3</v>
+        <v>66.02</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.3666666666666666</v>
+        <v>510.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.25</v>
+        <v>66.81</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.14</v>
+        <v>512.47</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1166666666666667</v>
+        <v>59.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.08571428571428572</v>
+        <v>512.39</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1</v>
+        <v>57.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.1</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.11</v>
+        <v>57.62</v>
       </c>
       <c r="AJ15" t="n">
-        <v>529.375</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>543.4333333333333</v>
+        <v>-0.03448275862068965</v>
       </c>
       <c r="AL15" t="n">
-        <v>540.475</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="AM15" t="n">
-        <v>533.17</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="AN15" t="n">
-        <v>532.825</v>
+        <v>0.03389830508474576</v>
       </c>
       <c r="AO15" t="n">
-        <v>530.8214285714286</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="AP15" t="n">
-        <v>531.8</v>
+        <v>0.02531645569620253</v>
       </c>
       <c r="AQ15" t="n">
-        <v>531.35</v>
+        <v>0.02247191011235955</v>
       </c>
       <c r="AR15" t="n">
-        <v>531.21</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="AS15" t="n">
-        <v>53.13599886141221</v>
+        <v>504.275</v>
       </c>
       <c r="AT15" t="n">
-        <v>58.50480512079518</v>
+        <v>501.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>68.79152836650745</v>
+        <v>508.0375</v>
       </c>
       <c r="AV15" t="n">
-        <v>76.21339186783382</v>
+        <v>505.44</v>
       </c>
       <c r="AW15" t="n">
-        <v>79.16161343521661</v>
+        <v>506.7416666666667</v>
       </c>
       <c r="AX15" t="n">
-        <v>80.79058182885488</v>
+        <v>507.7571428571429</v>
       </c>
       <c r="AY15" t="n">
-        <v>81.20535696615094</v>
+        <v>507.16875</v>
       </c>
       <c r="AZ15" t="n">
-        <v>80.06937790302719</v>
+        <v>507.7277777777778</v>
       </c>
       <c r="BA15" t="n">
-        <v>78.72735166382775</v>
+        <v>508.085</v>
       </c>
       <c r="BB15" t="n">
-        <v>451</v>
+        <v>35.69733008223444</v>
       </c>
       <c r="BC15" t="n">
-        <v>451</v>
+        <v>49.55542351751219</v>
       </c>
       <c r="BD15" t="n">
-        <v>438</v>
+        <v>59.48853749883249</v>
       </c>
       <c r="BE15" t="n">
-        <v>421</v>
+        <v>66.30736309038386</v>
       </c>
       <c r="BF15" t="n">
-        <v>421</v>
+        <v>67.38613801979025</v>
       </c>
       <c r="BG15" t="n">
-        <v>421</v>
+        <v>67.14747856435876</v>
       </c>
       <c r="BH15" t="n">
-        <v>421</v>
+        <v>66.27784526851714</v>
       </c>
       <c r="BI15" t="n">
-        <v>421</v>
+        <v>64.69645624466061</v>
       </c>
       <c r="BJ15" t="n">
-        <v>421</v>
+        <v>63.18574028212378</v>
       </c>
       <c r="BK15" t="n">
-        <v>644</v>
+        <v>446</v>
       </c>
       <c r="BL15" t="n">
-        <v>644</v>
+        <v>417</v>
       </c>
       <c r="BM15" t="n">
-        <v>651</v>
+        <v>410</v>
       </c>
       <c r="BN15" t="n">
-        <v>651</v>
+        <v>401</v>
       </c>
       <c r="BO15" t="n">
-        <v>651</v>
+        <v>401</v>
       </c>
       <c r="BP15" t="n">
-        <v>651</v>
+        <v>401</v>
       </c>
       <c r="BQ15" t="n">
-        <v>651</v>
+        <v>401</v>
       </c>
       <c r="BR15" t="n">
-        <v>651</v>
+        <v>401</v>
       </c>
       <c r="BS15" t="n">
-        <v>651</v>
+        <v>401</v>
       </c>
       <c r="BT15" t="n">
+        <v>632</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>632</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>632</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>632</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>632</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>632</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>632</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>632</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>632</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CG15" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.9090909090909091</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.7692307692307693</v>
+      <c r="CH15" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>514.8200000000001</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>57.62</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>520</v>
       </c>
       <c r="C16" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D16" t="n">
         <v>60</v>
-      </c>
-      <c r="D16" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E16" t="n">
         <v>520</v>
@@ -4296,966 +4813,1098 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>483.8982228540349</v>
-      </c>
-      <c r="J16" t="n">
-        <v>122.0904424461724</v>
-      </c>
-      <c r="K16" t="n">
-        <v>499.221907698625</v>
-      </c>
-      <c r="L16" t="n">
-        <v>102.7459529144392</v>
-      </c>
-      <c r="M16" t="n">
-        <v>505.8879562590668</v>
-      </c>
-      <c r="N16" t="n">
-        <v>97.77760403014685</v>
-      </c>
-      <c r="O16" t="n">
-        <v>507.4815328607164</v>
-      </c>
-      <c r="P16" t="n">
-        <v>83.30822363001437</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>510.8228895130449</v>
-      </c>
       <c r="R16" t="n">
-        <v>76.5553794884917</v>
+        <v>483.9</v>
       </c>
       <c r="S16" t="n">
-        <v>510.3425174091635</v>
+        <v>122.09</v>
       </c>
       <c r="T16" t="n">
-        <v>72.44524743637888</v>
+        <v>499.22</v>
       </c>
       <c r="U16" t="n">
-        <v>507.6206714020875</v>
+        <v>102.75</v>
       </c>
       <c r="V16" t="n">
-        <v>72.22922767705238</v>
+        <v>505.89</v>
       </c>
       <c r="W16" t="n">
-        <v>503.9279592067267</v>
+        <v>97.78</v>
       </c>
       <c r="X16" t="n">
-        <v>69.48004031247001</v>
+        <v>507.48</v>
       </c>
       <c r="Y16" t="n">
-        <v>509.2584798957203</v>
+        <v>83.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>70.52323437625037</v>
+        <v>510.82</v>
       </c>
       <c r="AA16" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>510.34</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>507.62</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>72.23</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>503.93</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>0.06</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
         <v>0</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AP16" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AQ16" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AR16" t="n">
         <v>0.01</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AS16" t="n">
         <v>484.3</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>493.1333333333333</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>501.125</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>500.78</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>500.5916666666666</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>502.0928571428572</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>504.2</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>504.5277777777778</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>504.975</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>65.59771337478159</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>68.69994339315151</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>74.92469135738899</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>77.96365563517401</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>79.02104106221049</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>77.59776289380028</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>75.96848030597953</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>74.33134754862893</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>72.91127741988889</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>383</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>383</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>383</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>383</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>383</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>383</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>383</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>383</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>383</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>654</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>654</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>654</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>654</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>654</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>654</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>654</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>654</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>654</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>1</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.25</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.8214285714285714</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.8275862068965517</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.8125</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>509.26</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>70.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G9_521_60_ABS1</t>
+          <t>S16_G9_519_62_ABS1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>91.91994069681246</v>
       </c>
       <c r="D17" t="n">
-        <v>88.95478131949592</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>517.0891930242898</v>
-      </c>
-      <c r="J17" t="n">
-        <v>80.66534883527221</v>
-      </c>
-      <c r="K17" t="n">
-        <v>525.1236330962975</v>
-      </c>
-      <c r="L17" t="n">
-        <v>68.14537962573567</v>
-      </c>
-      <c r="M17" t="n">
-        <v>531.3674550694143</v>
-      </c>
-      <c r="N17" t="n">
-        <v>89.96942804506318</v>
-      </c>
-      <c r="O17" t="n">
-        <v>534.6489724194171</v>
-      </c>
-      <c r="P17" t="n">
-        <v>73.75062621210968</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>529.2998952946099</v>
-      </c>
       <c r="R17" t="n">
-        <v>79.44020111010576</v>
+        <v>543.7</v>
       </c>
       <c r="S17" t="n">
-        <v>530.2397977119789</v>
+        <v>118.92</v>
       </c>
       <c r="T17" t="n">
-        <v>85.27096834759226</v>
+        <v>530.73</v>
       </c>
       <c r="U17" t="n">
-        <v>526.4738838468398</v>
+        <v>88.42</v>
       </c>
       <c r="V17" t="n">
-        <v>85.28177079693153</v>
+        <v>515.0700000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>525.32474189932</v>
+        <v>95.36</v>
       </c>
       <c r="X17" t="n">
-        <v>87.40592137275956</v>
+        <v>517.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>522.828076776284</v>
+        <v>89.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>92.66085197547739</v>
+        <v>524.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.15</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1</v>
+        <v>522.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.125</v>
+        <v>88.03</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1</v>
+        <v>521.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.08333333333333333</v>
+        <v>80.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.07142857142857142</v>
+        <v>519.24</v>
       </c>
       <c r="AG17" t="n">
+        <v>78.88</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>522.16</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="AP17" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH17" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>516.4</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>519.8333333333334</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>526.4375</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>527.5599999999999</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>528.8916666666667</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>530</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>528.68125</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>527.5222222222222</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="AR17" t="n">
-        <v>525.155</v>
+        <v>0.04</v>
       </c>
       <c r="AS17" t="n">
-        <v>66.9950744458128</v>
+        <v>554.975</v>
       </c>
       <c r="AT17" t="n">
-        <v>68.43857749024953</v>
+        <v>543.7333333333333</v>
       </c>
       <c r="AU17" t="n">
-        <v>71.87938573575876</v>
+        <v>526.3875</v>
       </c>
       <c r="AV17" t="n">
-        <v>74.61197222966298</v>
+        <v>525.66</v>
       </c>
       <c r="AW17" t="n">
-        <v>74.77675617388661</v>
+        <v>527.8583333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>75.9764061121233</v>
+        <v>525.6357142857142</v>
       </c>
       <c r="AY17" t="n">
-        <v>77.78081156967636</v>
+        <v>525.84375</v>
       </c>
       <c r="AZ17" t="n">
-        <v>79.22299438613877</v>
+        <v>525.2833333333333</v>
       </c>
       <c r="BA17" t="n">
-        <v>81.241190137762</v>
+        <v>524.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>371</v>
+        <v>66.56406218824088</v>
       </c>
       <c r="BC17" t="n">
-        <v>371</v>
+        <v>72.94127013487555</v>
       </c>
       <c r="BD17" t="n">
-        <v>371</v>
+        <v>79.66625599179366</v>
       </c>
       <c r="BE17" t="n">
-        <v>371</v>
+        <v>82.2186377897372</v>
       </c>
       <c r="BF17" t="n">
-        <v>371</v>
+        <v>83.78318206670252</v>
       </c>
       <c r="BG17" t="n">
-        <v>371</v>
+        <v>84.4529633003134</v>
       </c>
       <c r="BH17" t="n">
-        <v>371</v>
+        <v>83.91472955290686</v>
       </c>
       <c r="BI17" t="n">
-        <v>371</v>
+        <v>82.41111541803353</v>
       </c>
       <c r="BJ17" t="n">
-        <v>371</v>
+        <v>81.15300364127012</v>
       </c>
       <c r="BK17" t="n">
-        <v>617</v>
+        <v>467</v>
       </c>
       <c r="BL17" t="n">
-        <v>617</v>
+        <v>440</v>
       </c>
       <c r="BM17" t="n">
-        <v>632</v>
+        <v>412</v>
       </c>
       <c r="BN17" t="n">
-        <v>632</v>
+        <v>412</v>
       </c>
       <c r="BO17" t="n">
-        <v>632</v>
+        <v>412</v>
       </c>
       <c r="BP17" t="n">
-        <v>635</v>
+        <v>412</v>
       </c>
       <c r="BQ17" t="n">
-        <v>635</v>
+        <v>412</v>
       </c>
       <c r="BR17" t="n">
-        <v>635</v>
+        <v>412</v>
       </c>
       <c r="BS17" t="n">
-        <v>635</v>
+        <v>412</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.8</v>
+        <v>721</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.9</v>
+        <v>721</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.9166666666666666</v>
+        <v>721</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.8125</v>
+        <v>721</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.9545454545454546</v>
+        <v>721</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.9615384615384616</v>
+        <v>721</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.9</v>
+        <v>721</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.967741935483871</v>
+        <v>721</v>
       </c>
       <c r="CB17" t="n">
-        <v>0</v>
+        <v>721</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>522.16</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>79.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S18_G9_520_58_ABS1</t>
+          <t>S17_G9_521_60_ABS1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D18" t="n">
-        <v>85.9896219421794</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>535.383466604882</v>
-      </c>
-      <c r="J18" t="n">
-        <v>97.79336016752033</v>
-      </c>
-      <c r="K18" t="n">
-        <v>538.6716613650271</v>
-      </c>
-      <c r="L18" t="n">
-        <v>73.231495580519</v>
-      </c>
-      <c r="M18" t="n">
-        <v>521.851547527578</v>
-      </c>
-      <c r="N18" t="n">
-        <v>87.87033728335895</v>
-      </c>
-      <c r="O18" t="n">
-        <v>530.0046108153263</v>
-      </c>
-      <c r="P18" t="n">
-        <v>84.32864879280483</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>540.8207738863014</v>
-      </c>
       <c r="R18" t="n">
-        <v>88.20819974246885</v>
+        <v>517.09</v>
       </c>
       <c r="S18" t="n">
-        <v>534.4939080350081</v>
+        <v>80.67</v>
       </c>
       <c r="T18" t="n">
-        <v>85.19825979202271</v>
+        <v>525.12</v>
       </c>
       <c r="U18" t="n">
-        <v>538.7713787876804</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>83.87977815008907</v>
+        <v>531.37</v>
       </c>
       <c r="W18" t="n">
-        <v>536.5061746435607</v>
+        <v>89.97</v>
       </c>
       <c r="X18" t="n">
-        <v>80.94555457840521</v>
+        <v>534.65</v>
       </c>
       <c r="Y18" t="n">
-        <v>531.0542465801472</v>
+        <v>73.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>78.55663289810607</v>
+        <v>529.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.7</v>
+        <v>79.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5</v>
+        <v>530.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.325</v>
+        <v>85.27</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.24</v>
+        <v>526.47</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.2666666666666667</v>
+        <v>85.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.2</v>
+        <v>525.3200000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.175</v>
+        <v>87.41</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.1555555555555556</v>
+        <v>522.83</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.14</v>
+        <v>92.66</v>
       </c>
       <c r="AJ18" t="n">
-        <v>554.35</v>
+        <v>0.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>549.45</v>
+        <v>0.1</v>
       </c>
       <c r="AL18" t="n">
-        <v>539.125</v>
+        <v>0.125</v>
       </c>
       <c r="AM18" t="n">
-        <v>533.7</v>
+        <v>0.1</v>
       </c>
       <c r="AN18" t="n">
-        <v>540.2666666666667</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="AO18" t="n">
-        <v>536.8785714285714</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="AP18" t="n">
-        <v>536.39375</v>
+        <v>0.05</v>
       </c>
       <c r="AQ18" t="n">
-        <v>536.35</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="AR18" t="n">
-        <v>536.15</v>
+        <v>0.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>60.19200528309387</v>
+        <v>516.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>66.49597105589682</v>
+        <v>519.8333333333334</v>
       </c>
       <c r="AU18" t="n">
-        <v>69.60053430111007</v>
+        <v>526.4375</v>
       </c>
       <c r="AV18" t="n">
-        <v>74.41632885328326</v>
+        <v>527.5599999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>76.65732551788874</v>
+        <v>528.8916666666667</v>
       </c>
       <c r="AX18" t="n">
-        <v>79.61330361343447</v>
+        <v>530</v>
       </c>
       <c r="AY18" t="n">
-        <v>80.3752991343578</v>
+        <v>528.68125</v>
       </c>
       <c r="AZ18" t="n">
-        <v>80.8419909453002</v>
+        <v>527.5222222222222</v>
       </c>
       <c r="BA18" t="n">
-        <v>80.66236730966925</v>
+        <v>525.155</v>
       </c>
       <c r="BB18" t="n">
-        <v>452</v>
+        <v>66.9950744458128</v>
       </c>
       <c r="BC18" t="n">
-        <v>439</v>
+        <v>68.43857749024953</v>
       </c>
       <c r="BD18" t="n">
-        <v>424</v>
+        <v>71.87938573575876</v>
       </c>
       <c r="BE18" t="n">
-        <v>418</v>
+        <v>74.61197222966298</v>
       </c>
       <c r="BF18" t="n">
-        <v>418</v>
+        <v>74.77675617388661</v>
       </c>
       <c r="BG18" t="n">
-        <v>418</v>
+        <v>75.9764061121233</v>
       </c>
       <c r="BH18" t="n">
-        <v>418</v>
+        <v>77.78081156967636</v>
       </c>
       <c r="BI18" t="n">
-        <v>418</v>
+        <v>79.22299438613877</v>
       </c>
       <c r="BJ18" t="n">
-        <v>418</v>
+        <v>81.241190137762</v>
       </c>
       <c r="BK18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BL18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BM18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BN18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BO18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BP18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BQ18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BR18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BS18" t="n">
-        <v>713</v>
+        <v>371</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.8333333333333334</v>
+        <v>617</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.875</v>
+        <v>617</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.5</v>
+        <v>632</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.75</v>
+        <v>632</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.8421052631578947</v>
+        <v>632</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.95</v>
+        <v>635</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.84</v>
+        <v>635</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.8275862068965517</v>
+        <v>635</v>
       </c>
       <c r="CB18" t="n">
+        <v>635</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.8</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>522.83</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>92.66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S16_G9_519_62_ABS1</t>
+          <t>S18_G9_520_58_ABS1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D19" t="n">
-        <v>91.91994069681246</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F19" t="n">
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>543.6953335231638</v>
-      </c>
-      <c r="J19" t="n">
-        <v>118.9188273962207</v>
-      </c>
-      <c r="K19" t="n">
-        <v>530.7259146233664</v>
-      </c>
-      <c r="L19" t="n">
-        <v>88.42117425062764</v>
-      </c>
-      <c r="M19" t="n">
-        <v>515.0731741770232</v>
-      </c>
-      <c r="N19" t="n">
-        <v>95.35991236344047</v>
-      </c>
-      <c r="O19" t="n">
-        <v>517.0535586459451</v>
-      </c>
-      <c r="P19" t="n">
-        <v>89.27342870001685</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>524.34039580056</v>
-      </c>
       <c r="R19" t="n">
-        <v>93.70539897828498</v>
+        <v>535.38</v>
       </c>
       <c r="S19" t="n">
-        <v>522.3994891955049</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>88.02649253606977</v>
+        <v>538.67</v>
       </c>
       <c r="U19" t="n">
-        <v>521.0376854689822</v>
+        <v>73.23</v>
       </c>
       <c r="V19" t="n">
-        <v>80.94728563158009</v>
+        <v>521.85</v>
       </c>
       <c r="W19" t="n">
-        <v>519.2389063580105</v>
+        <v>87.87</v>
       </c>
       <c r="X19" t="n">
-        <v>78.87669299081369</v>
+        <v>530</v>
       </c>
       <c r="Y19" t="n">
-        <v>522.1566899151197</v>
+        <v>84.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>79.04787738930717</v>
+        <v>540.8200000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.4</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AB19" t="n">
+        <v>534.49</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>538.77</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>536.51</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>531.05</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AO19" t="n">
         <v>0.2</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0.04285714285714286</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>554.975</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>543.7333333333333</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>526.3875</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>525.66</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>527.8583333333333</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>525.6357142857142</v>
-      </c>
       <c r="AP19" t="n">
-        <v>525.84375</v>
+        <v>0.175</v>
       </c>
       <c r="AQ19" t="n">
-        <v>525.2833333333333</v>
+        <v>0.1555555555555556</v>
       </c>
       <c r="AR19" t="n">
-        <v>524.3</v>
+        <v>0.14</v>
       </c>
       <c r="AS19" t="n">
-        <v>66.56406218824088</v>
+        <v>554.35</v>
       </c>
       <c r="AT19" t="n">
-        <v>72.94127013487555</v>
+        <v>549.45</v>
       </c>
       <c r="AU19" t="n">
-        <v>79.66625599179366</v>
+        <v>539.125</v>
       </c>
       <c r="AV19" t="n">
-        <v>82.2186377897372</v>
+        <v>533.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>83.78318206670252</v>
+        <v>540.2666666666667</v>
       </c>
       <c r="AX19" t="n">
-        <v>84.4529633003134</v>
+        <v>536.8785714285714</v>
       </c>
       <c r="AY19" t="n">
-        <v>83.91472955290686</v>
+        <v>536.39375</v>
       </c>
       <c r="AZ19" t="n">
-        <v>82.41111541803353</v>
+        <v>536.35</v>
       </c>
       <c r="BA19" t="n">
-        <v>81.15300364127012</v>
+        <v>536.15</v>
       </c>
       <c r="BB19" t="n">
-        <v>467</v>
+        <v>60.19200528309387</v>
       </c>
       <c r="BC19" t="n">
-        <v>440</v>
+        <v>66.49597105589682</v>
       </c>
       <c r="BD19" t="n">
-        <v>412</v>
+        <v>69.60053430111007</v>
       </c>
       <c r="BE19" t="n">
-        <v>412</v>
+        <v>74.41632885328326</v>
       </c>
       <c r="BF19" t="n">
-        <v>412</v>
+        <v>76.65732551788874</v>
       </c>
       <c r="BG19" t="n">
-        <v>412</v>
+        <v>79.61330361343447</v>
       </c>
       <c r="BH19" t="n">
-        <v>412</v>
+        <v>80.3752991343578</v>
       </c>
       <c r="BI19" t="n">
-        <v>412</v>
+        <v>80.8419909453002</v>
       </c>
       <c r="BJ19" t="n">
-        <v>412</v>
+        <v>80.66236730966925</v>
       </c>
       <c r="BK19" t="n">
-        <v>721</v>
+        <v>452</v>
       </c>
       <c r="BL19" t="n">
-        <v>721</v>
+        <v>439</v>
       </c>
       <c r="BM19" t="n">
-        <v>721</v>
+        <v>424</v>
       </c>
       <c r="BN19" t="n">
-        <v>721</v>
+        <v>418</v>
       </c>
       <c r="BO19" t="n">
-        <v>721</v>
+        <v>418</v>
       </c>
       <c r="BP19" t="n">
-        <v>721</v>
+        <v>418</v>
       </c>
       <c r="BQ19" t="n">
-        <v>721</v>
+        <v>418</v>
       </c>
       <c r="BR19" t="n">
-        <v>721</v>
+        <v>418</v>
       </c>
       <c r="BS19" t="n">
-        <v>721</v>
+        <v>418</v>
       </c>
       <c r="BT19" t="n">
+        <v>713</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>713</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>713</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>713</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>713</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>713</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>713</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>713</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>713</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CE19" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU19" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="CA19" t="n">
+      <c r="CF19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CG19" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CB19" t="n">
-        <v>0.7804878048780488</v>
+      <c r="CH19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>531.05</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>78.56</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>521</v>
       </c>
       <c r="C20" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D20" t="n">
         <v>62</v>
-      </c>
-      <c r="D20" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E20" t="n">
         <v>521</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>513.3179708157639</v>
-      </c>
-      <c r="J20" t="n">
-        <v>109.3200926940524</v>
-      </c>
-      <c r="K20" t="n">
-        <v>523.3075892730192</v>
-      </c>
-      <c r="L20" t="n">
-        <v>76.97755955189945</v>
-      </c>
-      <c r="M20" t="n">
-        <v>524.3724037911649</v>
-      </c>
-      <c r="N20" t="n">
-        <v>67.54729894784033</v>
-      </c>
-      <c r="O20" t="n">
-        <v>521.8146393655906</v>
-      </c>
-      <c r="P20" t="n">
-        <v>68.93029187663591</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>513.5543558229967</v>
-      </c>
       <c r="R20" t="n">
-        <v>66.4657462848411</v>
+        <v>513.3200000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>515.3981654984372</v>
+        <v>109.32</v>
       </c>
       <c r="T20" t="n">
-        <v>67.70728333435899</v>
+        <v>523.3099999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>510.026048291131</v>
+        <v>76.98</v>
       </c>
       <c r="V20" t="n">
-        <v>70.22107273320223</v>
+        <v>524.37</v>
       </c>
       <c r="W20" t="n">
-        <v>508.7905160400827</v>
+        <v>67.55</v>
       </c>
       <c r="X20" t="n">
-        <v>71.99673215391543</v>
+        <v>521.8099999999999</v>
       </c>
       <c r="Y20" t="n">
-        <v>511.5397445246451</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>76.79297211896939</v>
+        <v>513.55</v>
       </c>
       <c r="AA20" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>510.03</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>508.79</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>72</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>511.54</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AK20" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AL20" t="n">
         <v>0.05</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AM20" t="n">
         <v>0.04</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AN20" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AO20" t="n">
         <v>0.01428571428571429</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AP20" t="n">
         <v>0</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AQ20" t="n">
         <v>-0.01111111111111111</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AR20" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AS20" t="n">
         <v>547.6</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>517.5666666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>517.575</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>519.3099999999999</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>519.1</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>518.0785714285714</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>516.3</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>514.5666666666667</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>515.085</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>41.5504512610874</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>62.65231218576233</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>66.47683337073148</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>66.79920583360254</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>66.45993780717323</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>66.64608742745335</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>67.11592582986545</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>67.92267662570431</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>69.3115991375181</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>453</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>429</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>429</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>429</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>429</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>429</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>427</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>419</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>419</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BT20" t="n">
         <v>635</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BU20" t="n">
         <v>635</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BV20" t="n">
         <v>635</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BW20" t="n">
         <v>635</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BX20" t="n">
         <v>635</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BY20" t="n">
         <v>635</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BZ20" t="n">
         <v>635</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="CA20" t="n">
         <v>635</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="CB20" t="n">
         <v>635</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="CC20" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>1</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.92</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.9285714285714286</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>511.54</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>521</v>
       </c>
       <c r="C21" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D21" t="n">
         <v>60</v>
-      </c>
-      <c r="D21" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E21" t="n">
         <v>521</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>534.9137243585004</v>
-      </c>
-      <c r="J21" t="n">
-        <v>51.05306794773674</v>
-      </c>
-      <c r="K21" t="n">
-        <v>522.2220210721588</v>
-      </c>
-      <c r="L21" t="n">
-        <v>50.10478637908272</v>
-      </c>
-      <c r="M21" t="n">
-        <v>525.3979591309558</v>
-      </c>
-      <c r="N21" t="n">
-        <v>49.26453188443432</v>
-      </c>
-      <c r="O21" t="n">
-        <v>525.3294452234758</v>
-      </c>
-      <c r="P21" t="n">
-        <v>52.02260344827097</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>528.0735515955009</v>
-      </c>
       <c r="R21" t="n">
-        <v>51.61254887690698</v>
+        <v>534.91</v>
       </c>
       <c r="S21" t="n">
-        <v>525.6425787419053</v>
+        <v>51.05</v>
       </c>
       <c r="T21" t="n">
-        <v>47.47139039219134</v>
+        <v>522.22</v>
       </c>
       <c r="U21" t="n">
-        <v>531.7207296141667</v>
+        <v>50.1</v>
       </c>
       <c r="V21" t="n">
-        <v>54.67188749363227</v>
+        <v>525.4</v>
       </c>
       <c r="W21" t="n">
-        <v>529.2089762713531</v>
+        <v>49.26</v>
       </c>
       <c r="X21" t="n">
-        <v>54.09911177768765</v>
+        <v>525.33</v>
       </c>
       <c r="Y21" t="n">
-        <v>529.263886995276</v>
+        <v>52.02</v>
       </c>
       <c r="Z21" t="n">
-        <v>57.07386376129747</v>
+        <v>528.0700000000001</v>
       </c>
       <c r="AA21" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>525.64</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>531.72</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>529.21</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>529.26</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>0.35</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AK21" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AL21" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AM21" t="n">
         <v>0.08</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AN21" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AO21" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AP21" t="n">
         <v>0.075</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AQ21" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AR21" t="n">
         <v>0.05</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
         <v>535.225</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>526.6166666666667</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>526.2875</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>525.95</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>526.6166666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>526.3285714285714</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>528.75</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>528.0166666666667</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>528.17</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>50.8451017798175</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>56.85920965175495</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>55.48675376835448</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>54.26884465326307</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>52.80927685759598</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>52.84498122637878</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>52.62508907355882</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>53.08603865424505</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>53.62500442890425</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>456</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>439</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>439</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>439</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>439</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>439</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>439</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>439</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>439</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>634</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>634</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>634</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>634</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>634</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>634</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>634</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>634</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>634</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>1</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.52</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.8275862068965517</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.8387096774193549</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>529.26</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>57.07</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>520.7</v>
       </c>
       <c r="C22" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D22" t="n">
         <v>60</v>
-      </c>
-      <c r="D22" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E22" t="n">
         <v>520.7</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.50225</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>76.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.879</v>
+      </c>
       <c r="I22" t="n">
-        <v>521.615513695082</v>
+        <v>2.833000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>79.21019080908417</v>
+        <v>2.801</v>
       </c>
       <c r="K22" t="n">
-        <v>522.1985737695397</v>
+        <v>2.7675</v>
       </c>
       <c r="L22" t="n">
-        <v>70.89410000525513</v>
+        <v>2.7625</v>
       </c>
       <c r="M22" t="n">
-        <v>521.2447852505718</v>
+        <v>2.752</v>
       </c>
       <c r="N22" t="n">
-        <v>72.74503797981558</v>
+        <v>2.8905</v>
       </c>
       <c r="O22" t="n">
-        <v>521.2202411228225</v>
+        <v>2.9395</v>
       </c>
       <c r="P22" t="n">
-        <v>71.48608034441006</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>523.4982442351647</v>
-      </c>
+        <v>2.941</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>71.63749871294161</v>
+        <v>521.6155</v>
       </c>
       <c r="S22" t="n">
-        <v>522.6821673304055</v>
+        <v>79.2105</v>
       </c>
       <c r="T22" t="n">
-        <v>71.1076762355259</v>
+        <v>522.1985000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>522.2499561439186</v>
+        <v>70.893</v>
       </c>
       <c r="V22" t="n">
-        <v>70.26222633399303</v>
+        <v>521.2450000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>521.1442038854732</v>
+        <v>72.74449999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>70.10412715416432</v>
+        <v>521.2194999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>521.2434964080405</v>
+        <v>71.4855</v>
       </c>
       <c r="Z22" t="n">
-        <v>69.71777057669834</v>
+        <v>523.4979999999999</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.2704588394062079</v>
+        <v>71.63849999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1594944476914085</v>
+        <v>522.6825</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.1106511684518014</v>
+        <v>71.108</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.08840507111935683</v>
+        <v>522.249</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.08867029862792575</v>
+        <v>70.26149999999998</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.07380319347006867</v>
+        <v>521.1445</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.06455223509274739</v>
+        <v>70.10550000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.05682523242594802</v>
+        <v>521.2435</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.04912580579666007</v>
+        <v>69.71799999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>524.31375</v>
+        <v>0.2705</v>
       </c>
       <c r="AK22" t="n">
-        <v>521.0816666666667</v>
+        <v>0.16</v>
       </c>
       <c r="AL22" t="n">
-        <v>520.9068750000001</v>
+        <v>0.111</v>
       </c>
       <c r="AM22" t="n">
-        <v>520.7860000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="AN22" t="n">
-        <v>522.3383333333334</v>
+        <v>0.08950000000000001</v>
       </c>
       <c r="AO22" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.05700000000000001</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>524.3154999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>521.0815</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>520.9075</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>520.7859999999999</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>522.3390000000001</v>
+      </c>
+      <c r="AX22" t="n">
         <v>522.35</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AY22" t="n">
         <v>522.3299999999999</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>522.1822222222222</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>521.986</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>58.24036579799679</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>63.20471400273787</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>66.22542219858478</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>68.61916368451861</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>69.44753692769186</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>70.09032083407773</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>70.21075969314157</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>70.10572757951402</v>
+        <v>522.1830000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>69.95290809780343</v>
+        <v>521.9849999999999</v>
       </c>
       <c r="BB22" t="n">
+        <v>58.24149999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>63.20450000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>66.2265</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>68.619</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>69.44800000000001</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>70.09100000000001</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>70.21199999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>70.10549999999999</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>69.953</v>
+      </c>
+      <c r="BK22" t="n">
         <v>411.15</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>401.2</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>396.4</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>394.35</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>394.2</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>393.75</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>393.65</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>393.25</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>393.25</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>647.05</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>648.05</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>649.75</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>650.2</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>651</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>651.6</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>651.6</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>651.65</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>651.8</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.817063492063492</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6819246031746031</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7420621045621046</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7907597592466014</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7583912704157689</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7938568490357669</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.813810896493233</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8228435904444483</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8040661612070235</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>521.2435</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>69.71799999999999</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.341640786499874</v>
       </c>
       <c r="C23" t="n">
+        <v>1.924049472269977</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.2977713690461</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.924049472269977</v>
       </c>
       <c r="E23" t="n">
         <v>1.341640786499874</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02124264578624802</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.891810605853835</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1949601848691433</v>
+      </c>
       <c r="I23" t="n">
-        <v>23.44576291462421</v>
+        <v>0.1991851822854935</v>
       </c>
       <c r="J23" t="n">
-        <v>36.1935502949458</v>
+        <v>0.2185333889941378</v>
       </c>
       <c r="K23" t="n">
-        <v>17.236575939121</v>
+        <v>0.223956645240476</v>
       </c>
       <c r="L23" t="n">
-        <v>19.07373789120409</v>
+        <v>0.2047302461391832</v>
       </c>
       <c r="M23" t="n">
-        <v>13.9505199531245</v>
+        <v>0.2024221747786177</v>
       </c>
       <c r="N23" t="n">
-        <v>18.39328180200554</v>
+        <v>0.2045913770884476</v>
       </c>
       <c r="O23" t="n">
-        <v>11.60361190334895</v>
+        <v>0.1751833625842243</v>
       </c>
       <c r="P23" t="n">
-        <v>13.76738391336018</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>10.76898415822874</v>
-      </c>
+        <v>0.1878381161924726</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>13.92895704343555</v>
+        <v>23.44520318462651</v>
       </c>
       <c r="S23" t="n">
-        <v>9.324474368660795</v>
+        <v>36.19299110325091</v>
       </c>
       <c r="T23" t="n">
-        <v>14.49203810703256</v>
+        <v>17.23653105745866</v>
       </c>
       <c r="U23" t="n">
-        <v>10.07694860948671</v>
+        <v>19.0752399722782</v>
       </c>
       <c r="V23" t="n">
-        <v>11.74640100087521</v>
+        <v>13.95138042594617</v>
       </c>
       <c r="W23" t="n">
-        <v>9.680883046547157</v>
+        <v>18.39355850491373</v>
       </c>
       <c r="X23" t="n">
-        <v>11.85230309249753</v>
+        <v>11.60247136786405</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.817585534427369</v>
+        <v>13.76752757492484</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.91375116711128</v>
+        <v>10.76894394470556</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.2797670354126844</v>
+        <v>13.92939084132994</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1915767445507102</v>
+        <v>9.323438418704152</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1204587300784167</v>
+        <v>14.49237389293526</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.07396471594807717</v>
+        <v>10.07675328873866</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.06808559618318717</v>
+        <v>11.74653511062999</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.05577448430827477</v>
+        <v>9.680824494573628</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.04709115177959775</v>
+        <v>11.85328090268238</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.04557917859716838</v>
+        <v>8.816762906979786</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.04295150493106863</v>
+        <v>11.91339962086036</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27.60407277706641</v>
+        <v>0.2790863854191311</v>
       </c>
       <c r="AK23" t="n">
-        <v>22.13683119422556</v>
+        <v>0.1922169826551562</v>
       </c>
       <c r="AL23" t="n">
-        <v>16.40845541567791</v>
+        <v>0.1216941809792503</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.07367067544859782</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.06847781046671826</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.05650104796419825</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.04498830257323622</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.04612340426565056</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.04388981418818818</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>27.60515807541086</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>22.13599314167813</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>16.40843553112079</v>
+      </c>
+      <c r="AV23" t="n">
         <v>13.54514960769119</v>
       </c>
-      <c r="AN23" t="n">
-        <v>12.76914724423795</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>10.77652598717735</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10.58562646537624</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>10.62114717822026</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>10.29226505682786</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>12.04058970690501</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.397793851819776</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.957200495555032</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.660448678543847</v>
-      </c>
       <c r="AW23" t="n">
-        <v>9.854596217954953</v>
+        <v>12.76989135674842</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.25412530584118</v>
+        <v>10.77734563551566</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.50201033540366</v>
+        <v>10.58482031272292</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10.16819855796913</v>
+        <v>10.61934634721484</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.953749288863019</v>
+        <v>10.29242874513514</v>
       </c>
       <c r="BB23" t="n">
+        <v>12.04022437061439</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8.397047397746425</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8.956662486369398</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.660646104577827</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>9.855486636493668</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>10.25497512122005</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>10.50097820004854</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>10.16746486800448</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.952495111647554</v>
+      </c>
+      <c r="BK23" t="n">
         <v>54.30157020119943</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>44.31775217556434</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>39.86741183367425</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>38.19930420970077</v>
       </c>
-      <c r="BF23" t="n">
-        <v>38.00775544128081</v>
-      </c>
-      <c r="BG23" t="n">
+      <c r="BO23" t="n">
+        <v>38.0077554412808</v>
+      </c>
+      <c r="BP23" t="n">
         <v>37.52455336527215</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>37.42821198817249</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>37.09429662502395</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>37.09429662502395</v>
       </c>
-      <c r="BK23" t="n">
-        <v>38.60389263164777</v>
-      </c>
-      <c r="BL23" t="n">
+      <c r="BT23" t="n">
+        <v>38.60389263164778</v>
+      </c>
+      <c r="BU23" t="n">
         <v>37.32146976290132</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>35.81513205630444</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>35.60987444368116</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>34.56344281097252</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>34.01145317931037</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>34.01145317931037</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>33.96325413706624</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>33.9389544856489</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.1681208687622491</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2478354556816225</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.1567929631222772</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.178833152179087</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2641903549406978</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2291792913140583</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.1561720646849246</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1984326523653777</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.2128348904117255</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>8.816762906979786</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>11.91339962086036</v>
       </c>
     </row>
   </sheetData>
